--- a/2026年6月20日 初回開発/04 UAT/UATシナリオ.xlsx
+++ b/2026年6月20日 初回開発/04 UAT/UATシナリオ.xlsx
@@ -10,7 +10,7 @@
     <sheet name="利用シナリオ" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'利用シナリオ'!$A$1:$F$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'利用シナリオ'!$A$1:$F$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -32,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -43,18 +43,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="002F5496"/>
         <bgColor rgb="002F5496"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
-        <bgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -70,18 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -449,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -909,71 +891,135 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>S-14</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>［既知の課題・参考］Bluetoothシャッター接続時の誤発火</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>対局中 → Bluetoothシャッター機器を新たに接続 → （想定外）音量キーイベントが誤発火 → 撮影 → 認識エラー → 自動中止</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>5回目UAT課題①で調査中の既知の問題。再現した場合は新規不具合として報告せず、診断用トーストの有無やlogcatの記録をお願いしたい</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>B-12（調査中・対応保留）</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>高（調査中）</t>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Bluetoothシャッター接続時に画面が初期化されないことの確認</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>対局中（またはキャリブレーション中）→ Bluetoothシャッター機器のスイッチをオン（ボタン操作はしない）→ 画面・進行状況がそのまま保たれる</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>6回目UAT課題①で根本解決（Android側のActivity再生成が原因と判明、configChangesで抑制）。退行していないことの確認</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>B-12</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>S-15</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>［未実装・参考］中断局の再開</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>棋譜一覧から中断局を選ぶ → 「対局再開」 → 棋譜通りに盤面を再現して撮影 → キャリブレーション → 対局再開</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>5回目UAT課題④で実現性検討中、現時点では未実装。実装後にこのシナリオを正式なテスト対象に追加する</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>（未実装）</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>（実装後に確定）</t>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>中断局の再開（盤面一致）</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>棋譜一覧から中断局（【対局中】【対局中止】【対局エラー中止】のいずれか）を選ぶ → 「対局再開」 → 中断時点の棋譜通りに盤面を再現して撮影 → 赤丸自動検出 or 手動タップ → 盤面一致 → 対局再開（手数・game_idは継続） → 続きの手を撮影 → 終局</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5回目UAT課題④で実装済み。中断局からの継続が正しく動き、手数や持ち駒（KIF側から引き継ぎ）が壊れないこと</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>G-01</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>S-16</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>中断局の再開（盤面不一致→このまま進める）</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>S-15と同じ前提 → 撮影した盤面が中断時点の棋譜と一致しない（駒の並べ間違い等） → グリッド確認画面で不一致件数を見て「このまま進める」 → 対局再開 → 続きの手を撮影</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>不一致でも人間が判断して進められること、認識結果を正として以後の手の差分判定が正しく続くこと</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>G-02</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>S-17</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>中断局の再開（盤面不一致→手動タップで直す）</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>S-16と同じ状況 → 「手動タップで直す」を選び、同じ写真のまま盤の四隅をタップ → グリッド確認OK → 対局再開</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>撮り直しなしで手動補正に切り替えられ、その後の対局再開が正しく動くこと</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>G-03</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F16"/>
+  <autoFilter ref="A1:F18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/2026年6月20日 初回開発/04 UAT/UATシナリオ.xlsx
+++ b/2026年6月20日 初回開発/04 UAT/UATシナリオ.xlsx
@@ -10,7 +10,7 @@
     <sheet name="利用シナリオ" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'利用シナリオ'!$A$1:$F$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'利用シナリオ'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1018,8 +1018,40 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>S-18</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>ブラウザから棋譜を確認・共有する</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>PCまたはスマホのブラウザで http://&lt;サーバーIP&gt;:8000/web を開く → 一覧表示（日付絞り込み可） → 対局を選んでKIF詳細を確認 → 「共有」または「コピー（分析Tool貼付用）」 → 一覧に戻る</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Androidアプリを使わず、ブラウザだけで棋譜の確認・共有ができること。対局再開ボタンは表示されないこと（PC等からの再開は非対応）</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>C-08,C-09,C-10,C-11</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F18"/>
+  <autoFilter ref="A1:F19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>